--- a/fleet-report-app/data/fleet_utilization.xlsx
+++ b/fleet-report-app/data/fleet_utilization.xlsx
@@ -1,47 +1,236 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Fleet" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Fleet" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+  <si>
+    <t>Boat Name</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Berth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Hours This Month</t>
+  </si>
+  <si>
+    <t>Last Used</t>
+  </si>
+  <si>
+    <t>Fuel %</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Destination Latitude</t>
+  </si>
+  <si>
+    <t>Destination Longitude</t>
+  </si>
+  <si>
+    <t>Sea Falcon</t>
+  </si>
+  <si>
+    <t>RIB</t>
+  </si>
+  <si>
+    <t>Pier 3 - A12</t>
+  </si>
+  <si>
+    <t>In Use</t>
+  </si>
+  <si>
+    <t>J. Mercer</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>Northern Star</t>
+  </si>
+  <si>
+    <t>Yacht</t>
+  </si>
+  <si>
+    <t>Pier 1 - B04</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>Blue Horizon</t>
+  </si>
+  <si>
+    <t>Catamaran</t>
+  </si>
+  <si>
+    <t>Pier 2 - C01</t>
+  </si>
+  <si>
+    <t>A. Nilsen</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>Wave Runner</t>
+  </si>
+  <si>
+    <t>Speedboat</t>
+  </si>
+  <si>
+    <t>Pier 3 - A08</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>Coral Drifter</t>
+  </si>
+  <si>
+    <t>Tender</t>
+  </si>
+  <si>
+    <t>Pier 4 - D02</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>Storm Petrel</t>
+  </si>
+  <si>
+    <t>Pier 3 - A14</t>
+  </si>
+  <si>
+    <t>K. Solberg</t>
+  </si>
+  <si>
+    <t>Ocean Pearl</t>
+  </si>
+  <si>
+    <t>Pier 1 - B02</t>
+  </si>
+  <si>
+    <t>Reserved</t>
+  </si>
+  <si>
+    <t>T. Bakke</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>Windward</t>
+  </si>
+  <si>
+    <t>Pier 2 - C05</t>
+  </si>
+  <si>
+    <t>M. Iversen</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>Riptide</t>
+  </si>
+  <si>
+    <t>Pier 3 - A10</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>Sunfish</t>
+  </si>
+  <si>
+    <t>Pier 4 - D06</t>
+  </si>
+  <si>
+    <t>R. Haugen</t>
+  </si>
+  <si>
+    <t>Harbor Ghost</t>
+  </si>
+  <si>
+    <t>Pier 3 - A16</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>Pier 1 - B06</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>Kestrel</t>
+  </si>
+  <si>
+    <t>Pier 3 - A18</t>
+  </si>
+  <si>
+    <t>Tidewater</t>
+  </si>
+  <si>
+    <t>Pier 2 - C08</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>Marlin</t>
+  </si>
+  <si>
+    <t>Pier 4 - D09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +254,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,428 +593,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Boat Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Berth</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Assigned To</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Hours This Month</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Last Used</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Fuel %</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Sea Falcon</v>
-      </c>
-      <c r="B2" t="str">
-        <v>RIB</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pier 3 - A12</v>
-      </c>
-      <c r="D2" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E2" t="str">
-        <v>J. Mercer</v>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
       <c r="F2">
         <v>42</v>
       </c>
-      <c r="G2" t="str">
-        <v>2026-08-20</v>
+      <c r="G2" t="s">
+        <v>17</v>
       </c>
       <c r="H2">
         <v>65</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Northern Star</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Yacht</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Pier 1 - B04</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Idle</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
+      <c r="I2">
+        <v>59.90166</v>
+      </c>
+      <c r="J2">
+        <v>10.71794</v>
+      </c>
+      <c r="K2">
+        <v>59.91067</v>
+      </c>
+      <c r="L2">
+        <v>10.71802</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3" t="str">
-        <v>2026-07-30</v>
+      <c r="G3" t="s">
+        <v>22</v>
       </c>
       <c r="H3">
         <v>90</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Blue Horizon</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Catamaran</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pier 2 - C01</v>
-      </c>
-      <c r="D4" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A. Nilsen</v>
+      <c r="I3">
+        <v>59.91144</v>
+      </c>
+      <c r="J3">
+        <v>10.6952</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
       </c>
       <c r="F4">
         <v>55</v>
       </c>
-      <c r="G4" t="str">
-        <v>2026-08-21</v>
+      <c r="G4" t="s">
+        <v>27</v>
       </c>
       <c r="H4">
         <v>40</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Wave Runner</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Speedboat</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Pier 3 - A08</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Maintenance</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="I4">
+        <v>59.88263</v>
+      </c>
+      <c r="J4">
+        <v>10.68759</v>
+      </c>
+      <c r="K4">
+        <v>59.89604</v>
+      </c>
+      <c r="L4">
+        <v>10.73218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5" t="str">
-        <v>2026-08-05</v>
+      <c r="G5" t="s">
+        <v>32</v>
       </c>
       <c r="H5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Coral Drifter</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Tender</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Pier 4 - D02</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Idle</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
+      <c r="I5">
+        <v>59.91261</v>
+      </c>
+      <c r="J5">
+        <v>10.69753</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" t="str">
-        <v>2026-06-18</v>
+      <c r="G6" t="s">
+        <v>36</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Storm Petrel</v>
-      </c>
-      <c r="B7" t="str">
-        <v>RIB</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Pier 3 - A14</v>
-      </c>
-      <c r="D7" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E7" t="str">
-        <v>K. Solberg</v>
+      <c r="I6">
+        <v>59.91144</v>
+      </c>
+      <c r="J6">
+        <v>10.69753</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
       </c>
       <c r="F7">
         <v>61</v>
       </c>
-      <c r="G7" t="str">
-        <v>2026-08-21</v>
+      <c r="G7" t="s">
+        <v>27</v>
       </c>
       <c r="H7">
         <v>55</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Ocean Pearl</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Yacht</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Pier 1 - B02</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Reserved</v>
-      </c>
-      <c r="E8" t="str">
-        <v>T. Bakke</v>
+      <c r="I7">
+        <v>59.9022</v>
+      </c>
+      <c r="J7">
+        <v>10.70802</v>
+      </c>
+      <c r="K7">
+        <v>59.90314</v>
+      </c>
+      <c r="L7">
+        <v>10.69871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
       </c>
       <c r="F8">
         <v>12</v>
       </c>
-      <c r="G8" t="str">
-        <v>2026-08-15</v>
+      <c r="G8" t="s">
+        <v>44</v>
       </c>
       <c r="H8">
         <v>80</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Windward</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Catamaran</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Pier 2 - C05</v>
-      </c>
-      <c r="D9" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E9" t="str">
-        <v>M. Iversen</v>
+      <c r="I8">
+        <v>59.87899</v>
+      </c>
+      <c r="J8">
+        <v>10.67073</v>
+      </c>
+      <c r="K8">
+        <v>59.9096</v>
+      </c>
+      <c r="L8">
+        <v>10.72274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
       </c>
       <c r="F9">
         <v>38</v>
       </c>
-      <c r="G9" t="str">
-        <v>2026-08-19</v>
+      <c r="G9" t="s">
+        <v>48</v>
       </c>
       <c r="H9">
         <v>70</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Riptide</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Speedboat</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Pier 3 - A10</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Idle</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
+      <c r="I9">
+        <v>59.88771</v>
+      </c>
+      <c r="J9">
+        <v>10.67425</v>
+      </c>
+      <c r="K9">
+        <v>59.89079</v>
+      </c>
+      <c r="L9">
+        <v>10.69425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
-      <c r="G10" t="str">
-        <v>2026-07-25</v>
+      <c r="G10" t="s">
+        <v>51</v>
       </c>
       <c r="H10">
         <v>95</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Sunfish</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Tender</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Pier 4 - D06</v>
-      </c>
-      <c r="D11" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E11" t="str">
-        <v>R. Haugen</v>
+      <c r="I10">
+        <v>59.91144</v>
+      </c>
+      <c r="J10">
+        <v>10.69986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
       </c>
       <c r="F11">
         <v>29</v>
       </c>
-      <c r="G11" t="str">
-        <v>2026-08-20</v>
+      <c r="G11" t="s">
+        <v>17</v>
       </c>
       <c r="H11">
         <v>60</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Harbor Ghost</v>
-      </c>
-      <c r="B12" t="str">
-        <v>RIB</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Pier 3 - A16</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Maintenance</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
+      <c r="I11">
+        <v>59.88088</v>
+      </c>
+      <c r="J11">
+        <v>10.70455</v>
+      </c>
+      <c r="K11">
+        <v>59.88958</v>
+      </c>
+      <c r="L11">
+        <v>10.74051</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" t="str">
-        <v>2026-08-02</v>
+      <c r="G12" t="s">
+        <v>57</v>
       </c>
       <c r="H12">
         <v>15</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Aurora</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Yacht</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Pier 1 - B06</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Idle</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
+      <c r="I12">
+        <v>59.91378</v>
+      </c>
+      <c r="J12">
+        <v>10.6952</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
       </c>
       <c r="F13">
         <v>8</v>
       </c>
-      <c r="G13" t="str">
-        <v>2026-08-01</v>
+      <c r="G13" t="s">
+        <v>60</v>
       </c>
       <c r="H13">
         <v>85</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Kestrel</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Speedboat</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Pier 3 - A18</v>
-      </c>
-      <c r="D14" t="str">
-        <v>In Use</v>
-      </c>
-      <c r="E14" t="str">
-        <v>J. Mercer</v>
+      <c r="I13">
+        <v>59.91144</v>
+      </c>
+      <c r="J13">
+        <v>10.70219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
       </c>
       <c r="F14">
         <v>47</v>
       </c>
-      <c r="G14" t="str">
-        <v>2026-08-21</v>
+      <c r="G14" t="s">
+        <v>27</v>
       </c>
       <c r="H14">
         <v>50</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Tidewater</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Catamaran</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Pier 2 - C08</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Reserved</v>
-      </c>
-      <c r="E15" t="str">
-        <v>A. Nilsen</v>
+      <c r="I14">
+        <v>59.87677</v>
+      </c>
+      <c r="J14">
+        <v>10.71849</v>
+      </c>
+      <c r="K14">
+        <v>59.89195</v>
+      </c>
+      <c r="L14">
+        <v>10.7133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
       </c>
       <c r="F15">
         <v>15</v>
       </c>
-      <c r="G15" t="str">
-        <v>2026-08-14</v>
+      <c r="G15" t="s">
+        <v>65</v>
       </c>
       <c r="H15">
         <v>75</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Marlin</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Tender</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Pier 4 - D09</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Idle</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
+      <c r="I15">
+        <v>59.89746</v>
+      </c>
+      <c r="J15">
+        <v>10.7439</v>
+      </c>
+      <c r="K15">
+        <v>59.9096</v>
+      </c>
+      <c r="L15">
+        <v>10.72274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" t="str">
-        <v>2026-07-10</v>
+      <c r="G16" t="s">
+        <v>68</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
+      <c r="I16">
+        <v>59.91261</v>
+      </c>
+      <c r="J16">
+        <v>10.6952</v>
+      </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
-  </ignoredErrors>
 </worksheet>
 </file>